--- a/artfynd/A 11405-2024 artfynd.xlsx
+++ b/artfynd/A 11405-2024 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>121326321</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11405-2024 artfynd.xlsx
+++ b/artfynd/A 11405-2024 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>121326321</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11405-2024 artfynd.xlsx
+++ b/artfynd/A 11405-2024 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>121326321</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11405-2024 artfynd.xlsx
+++ b/artfynd/A 11405-2024 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>121326321</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11405-2024 artfynd.xlsx
+++ b/artfynd/A 11405-2024 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>121326321</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11405-2024 artfynd.xlsx
+++ b/artfynd/A 11405-2024 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>121326321</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11405-2024 artfynd.xlsx
+++ b/artfynd/A 11405-2024 artfynd.xlsx
@@ -1350,7 +1350,7 @@
         <v>121326321</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 11405-2024 artfynd.xlsx
+++ b/artfynd/A 11405-2024 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116192040</v>
+        <v>116192611</v>
       </c>
       <c r="B2" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stortallen (Stortallen), Upl</t>
+          <t>Stortallen, Stortallen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681164</v>
+        <v>681171</v>
       </c>
       <c r="R2" t="n">
-        <v>6589023</v>
+        <v>6589038</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116189249</v>
+        <v>116192040</v>
       </c>
       <c r="B3" t="n">
-        <v>97735</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stortallen (Stortallen), Upl</t>
+          <t>Stortallen, Stortallen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681046</v>
+        <v>681164</v>
       </c>
       <c r="R3" t="n">
-        <v>6588919</v>
+        <v>6589023</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116187753</v>
+        <v>116192047</v>
       </c>
       <c r="B4" t="n">
-        <v>104822</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stortallen (Stortallen), Upl</t>
+          <t>Stortallen, Stortallen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680971</v>
+        <v>681173</v>
       </c>
       <c r="R4" t="n">
-        <v>6588878</v>
+        <v>6588971</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116189112</v>
+        <v>116189249</v>
       </c>
       <c r="B5" t="n">
-        <v>96695</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stortallen (Stortallen), Upl</t>
+          <t>Stortallen, Stortallen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681009</v>
+        <v>681046</v>
       </c>
       <c r="R5" t="n">
-        <v>6588943</v>
+        <v>6588919</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,53 +1103,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116192047</v>
+        <v>121326321</v>
       </c>
       <c r="B6" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stortallen (Stortallen), Upl</t>
+          <t>Stortallen, Bogesundslandet (*knärot* /stjälk/), Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681173</v>
+        <v>681045</v>
       </c>
       <c r="R6" t="n">
-        <v>6588971</v>
+        <v>6588918</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,24 +1175,24 @@
           <t>Östra Ryd</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>AB-Vax-0025</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>2024-04-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-04-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:45</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stortallen, Obskoord: 6589007/1635406/5 m ().</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,62 +1207,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116192611</v>
+        <v>116187753</v>
       </c>
       <c r="B7" t="n">
-        <v>90417</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stortallen (Stortallen), Upl</t>
+          <t>Stortallen, Stortallen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681171</v>
+        <v>680971</v>
       </c>
       <c r="R7" t="n">
-        <v>6589038</v>
+        <v>6588878</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1303,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,62 +1330,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121326321</v>
+        <v>116189112</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stortallen, Bogesundslandet (*knärot* /stjälk/), Upl</t>
+          <t>Stortallen, Stortallen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681045</v>
+        <v>681009</v>
       </c>
       <c r="R8" t="n">
-        <v>6588918</v>
+        <v>6588943</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,24 +1393,24 @@
           <t>Östra Ryd</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>AB-Vax-0025</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>2024-04-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-04-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stortallen, Obskoord: 6589007/1635406/5 m ().</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1425,7 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -1464,11 +1433,7 @@
           <t>Olle Finnström</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
